--- a/data/trans_bre/P20B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 19,09</t>
+          <t>-7,91; 18,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 12,92</t>
+          <t>-12,18; 12,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 22,37</t>
+          <t>-10,3; 23,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 4,08</t>
+          <t>-24,32; 2,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 110,86</t>
+          <t>-22,88; 102,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 58,63</t>
+          <t>-35,02; 61,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 107,21</t>
+          <t>-28,11; 112,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,54; 16,09</t>
+          <t>-56,57; 12,95</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 3,19</t>
+          <t>-22,83; 3,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 0,94</t>
+          <t>-22,58; 1,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,01; -4,84</t>
+          <t>-31,25; -4,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 2,14</t>
+          <t>-23,57; 1,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,87; 29,88</t>
+          <t>-73,63; 35,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 4,3</t>
+          <t>-57,08; 9,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,19; -11,4</t>
+          <t>-62,38; -13,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,99; 7,94</t>
+          <t>-53,26; 6,31</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 0,47</t>
+          <t>-51,57; -3,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 23,21</t>
+          <t>-36,94; 22,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 0,35</t>
+          <t>-32,44; 1,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 6,14</t>
+          <t>-29,95; 5,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-92,17; 17,39</t>
+          <t>-92,94; 6,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,75; —</t>
+          <t>-82,92; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 170,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,27; 37,5</t>
+          <t>-72,74; 32,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 1,92</t>
+          <t>-14,9; 2,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 3,16</t>
+          <t>-13,02; 3,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 0,05</t>
+          <t>-18,99; 0,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,31; -0,38</t>
+          <t>-18,67; -1,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 10,86</t>
+          <t>-47,18; 13,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 13,98</t>
+          <t>-38,34; 13,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 0,31</t>
+          <t>-48,1; 2,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,39; -0,74</t>
+          <t>-47,85; -5,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20B-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P20B-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-9,59</t>
+          <t>-8,38</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-28,45%</t>
+          <t>-25,06%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 18,06</t>
+          <t>-8,17; 18,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 12,83</t>
+          <t>-11,22; 12,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 23,15</t>
+          <t>-10,31; 25,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 2,62</t>
+          <t>-23,0; 5,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 102,52</t>
+          <t>-23,02; 106,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 61,84</t>
+          <t>-31,97; 60,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 112,86</t>
+          <t>-24,28; 122,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,57; 12,95</t>
+          <t>-54,52; 24,85</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-10,17</t>
+          <t>-11,61</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-29,36%</t>
+          <t>-32,65%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 3,86</t>
+          <t>-23,76; 3,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 1,67</t>
+          <t>-21,6; 1,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,25; -4,59</t>
+          <t>-32,15; -4,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 1,03</t>
+          <t>-23,38; 0,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,63; 35,7</t>
+          <t>-74,32; 27,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,08; 9,32</t>
+          <t>-56,64; 7,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -13,0</t>
+          <t>-63,93; -14,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 6,31</t>
+          <t>-55,07; 0,8</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-11,59</t>
+          <t>-8,89</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-40,02%</t>
+          <t>-32,16%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-51,57; -3,02</t>
+          <t>-49,18; -0,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 22,34</t>
+          <t>-44,06; 23,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 1,42</t>
+          <t>-31,94; 1,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 5,36</t>
+          <t>-28,66; 7,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-92,94; 6,68</t>
+          <t>-91,67; 18,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,92; —</t>
+          <t>-86,18; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 170,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,74; 32,29</t>
+          <t>-71,16; 49,43</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,31</t>
+          <t>-10,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-31,03%</t>
+          <t>-30,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 2,69</t>
+          <t>-14,99; 2,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 3,29</t>
+          <t>-12,89; 3,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 0,61</t>
+          <t>-18,67; -0,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -1,79</t>
+          <t>-18,91; -2,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 13,67</t>
+          <t>-47,19; 14,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 13,88</t>
+          <t>-36,44; 16,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 2,99</t>
+          <t>-46,47; -0,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,85; -5,53</t>
+          <t>-48,98; -7,38</t>
         </is>
       </c>
     </row>
